--- a/data/trans_camb/IP16A03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 1,87</t>
+          <t>-34,34; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 5,99</t>
+          <t>-30,26; 5,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,02; -4,51</t>
+          <t>-35,59; -4,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 19,99</t>
+          <t>-13,25; 19,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 23,5</t>
+          <t>-13,74; 21,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 7,33</t>
+          <t>-25,25; 7,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 5,35</t>
+          <t>-17,64; 6,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 8,64</t>
+          <t>-15,01; 9,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -0,6</t>
+          <t>-21,84; -0,43</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,89; 273,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 0,0</t>
+          <t>-19,17; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 0,0</t>
+          <t>-19,57; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 0,0</t>
+          <t>-19,59; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 9,69</t>
+          <t>-16,21; 10,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 0,0</t>
+          <t>-24,51; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 0,0</t>
+          <t>-23,04; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 4,0</t>
+          <t>-12,94; 3,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 0,0</t>
+          <t>-17,02; -1,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 0,0</t>
+          <t>-15,58; -1,76</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 7,53</t>
+          <t>-30,51; 4,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 0,0</t>
+          <t>-36,37; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 9,73</t>
+          <t>-30,21; 8,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 0,0</t>
+          <t>-29,77; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 0,0</t>
+          <t>-29,75; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 0,0</t>
+          <t>-29,68; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 0,55</t>
+          <t>-20,44; 0,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,51; -2,94</t>
+          <t>-24,81; -2,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 1,89</t>
+          <t>-21,01; 1,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 4,67</t>
+          <t>-12,71; 4,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 0,0</t>
+          <t>-19,08; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 0,0</t>
+          <t>-18,86; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 0,0</t>
+          <t>-24,05; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 0,0</t>
+          <t>-28,35; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 0,0</t>
+          <t>-21,66; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 1,29</t>
+          <t>-12,93; 1,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 0,0</t>
+          <t>-14,41; 0,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 0,0</t>
+          <t>-13,91; 0,0</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,36</t>
+          <t>0,0; 22,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,11</t>
+          <t>0,0; 29,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,92</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,23</t>
+          <t>0,0; 19,16</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 12,28</t>
+          <t>-30,42; 10,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-38,11; -4,91</t>
+          <t>-40,51; -4,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-38,11; -4,91</t>
+          <t>-40,51; -4,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 5,12</t>
+          <t>-28,27; 5,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 0,0</t>
+          <t>-33,96; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 0,0</t>
+          <t>-34,28; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 2,33</t>
+          <t>-22,08; 2,41</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-29,8; -5,34</t>
+          <t>-28,02; -5,2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-27,92; -5,33</t>
+          <t>-27,56; -5,32</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,6</t>
+          <t>-100,0; 182,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,35; 29,62</t>
+          <t>7,27; 29,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>0,0; 26,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,48; 19,39</t>
+          <t>1,41; 19,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 7,53</t>
+          <t>-19,77; 8,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 21,96</t>
+          <t>-16,24; 22,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 9,22</t>
+          <t>-18,72; 8,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 14,46</t>
+          <t>-4,76; 14,0</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 14,0</t>
+          <t>-8,96; 12,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 9,37</t>
+          <t>-7,74; 8,7</t>
         </is>
       </c>
     </row>
@@ -2094,32 +2094,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 191,47</t>
+          <t>-100,0; 243,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 518,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 231,62</t>
+          <t>-83,98; 208,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 587,09</t>
+          <t>-49,45; 460,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 500,16</t>
+          <t>-100,0; 471,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-70,34; 446,03</t>
+          <t>-66,93; 303,24</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 0,0</t>
+          <t>-13,7; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 9,06</t>
+          <t>-7,47; 8,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 0,0</t>
+          <t>-15,64; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -1,51</t>
+          <t>-13,4; -1,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 18,79</t>
+          <t>-4,07; 18,86</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -1,48</t>
+          <t>-13,16; -1,51</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,91; -1,63</t>
+          <t>-10,9; -1,88</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 11,85</t>
+          <t>-4,07; 10,23</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -1,63</t>
+          <t>-10,3; -1,83</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,24; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 519,71</t>
+          <t>-69,22; 500,41</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 2,86</t>
+          <t>-5,49; 3,27</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -0,57</t>
+          <t>-7,97; -0,52</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -0,99</t>
+          <t>-8,24; -0,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,97</t>
+          <t>-7,83; 1,14</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,96</t>
+          <t>-6,8; 3,05</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 0,07</t>
+          <t>-8,41; 0,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 0,59</t>
+          <t>-5,69; 0,45</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,17</t>
+          <t>-6,49; -0,31</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,04; -1,42</t>
+          <t>-7,11; -1,59</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 90,41</t>
+          <t>-68,85; 107,12</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-93,58; -1,78</t>
+          <t>-92,15; 0,77</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-94,44; -0,94</t>
+          <t>-93,67; -9,51</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-81,08; 34,68</t>
+          <t>-80,01; 44,86</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-75,28; 48,75</t>
+          <t>-70,34; 75,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 10,49</t>
+          <t>-83,04; 7,25</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 15,17</t>
+          <t>-66,01; 11,72</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-74,82; -2,17</t>
+          <t>-75,59; 2,93</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-82,26; -27,05</t>
+          <t>-82,41; -29,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 1,85</t>
+          <t>-34,21; 0,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 5,29</t>
+          <t>-30,32; 4,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,59; -4,6</t>
+          <t>-39,72; -4,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 19,86</t>
+          <t>-13,36; 19,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 21,71</t>
+          <t>-13,45; 22,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 7,84</t>
+          <t>-26,71; 7,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 6,72</t>
+          <t>-17,81; 5,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 9,84</t>
+          <t>-16,5; 9,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -0,43</t>
+          <t>-23,75; -0,52</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,69; 292,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 0,0</t>
+          <t>-17,66; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 0,0</t>
+          <t>-19,38; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 0,0</t>
+          <t>-19,37; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 10,92</t>
+          <t>-17,0; 9,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 0,0</t>
+          <t>-21,89; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 0,0</t>
+          <t>-24,05; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 3,8</t>
+          <t>-11,47; 4,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -1,76</t>
+          <t>-15,65; -1,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -1,76</t>
+          <t>-15,7; -1,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 4,74</t>
+          <t>-31,63; 7,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 0,0</t>
+          <t>-36,92; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 8,32</t>
+          <t>-30,22; 9,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 0,0</t>
+          <t>-32,8; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 0,0</t>
+          <t>-29,82; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 0,0</t>
+          <t>-33,16; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 0,67</t>
+          <t>-22,02; 0,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,81; -2,85</t>
+          <t>-22,75; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 1,84</t>
+          <t>-19,65; 2,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 4,6</t>
+          <t>-12,8; 4,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 0,0</t>
+          <t>-15,96; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 0,0</t>
+          <t>-16,25; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 0,0</t>
+          <t>-23,72; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 0,0</t>
+          <t>-24,32; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 0,0</t>
+          <t>-23,7; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 1,34</t>
+          <t>-11,8; 2,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 0,0</t>
+          <t>-13,46; 0,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 0,0</t>
+          <t>-13,17; 0,0</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,98</t>
+          <t>0,0; 28,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,23</t>
+          <t>0,0; 29,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 10,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,16</t>
+          <t>0,0; 18,72</t>
         </is>
       </c>
     </row>
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 10,66</t>
+          <t>-31,39; 10,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-40,51; -4,89</t>
+          <t>-38,32; -4,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-40,51; -4,89</t>
+          <t>-38,32; -4,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 5,37</t>
+          <t>-27,97; 6,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 0,0</t>
+          <t>-34,26; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 2,41</t>
+          <t>-21,86; 4,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -5,2</t>
+          <t>-27,68; -5,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-27,56; -5,32</t>
+          <t>-27,34; -5,23</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 182,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,27; 29,43</t>
+          <t>5,41; 28,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,11</t>
+          <t>0,0; 23,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,41; 19,27</t>
+          <t>1,38; 16,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 8,19</t>
+          <t>-21,16; 5,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 22,76</t>
+          <t>-17,74; 21,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 8,46</t>
+          <t>-18,42; 8,88</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 14,0</t>
+          <t>-5,04; 14,49</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 12,97</t>
+          <t>-8,95; 12,83</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 8,7</t>
+          <t>-8,01; 9,03</t>
         </is>
       </c>
     </row>
@@ -2094,32 +2094,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 243,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 518,95</t>
+          <t>-100,0; 442,78</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-83,98; 208,03</t>
+          <t>-85,59; 185,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 460,51</t>
+          <t>-50,86; 562,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 471,18</t>
+          <t>-100,0; 433,19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 303,24</t>
+          <t>-68,38; 292,05</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 0,0</t>
+          <t>-12,63; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 8,86</t>
+          <t>-6,74; 9,47</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 0,0</t>
+          <t>-15,69; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,4; -1,51</t>
+          <t>-13,25; -1,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 18,86</t>
+          <t>-3,95; 18,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -1,51</t>
+          <t>-13,84; -1,52</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,9; -1,88</t>
+          <t>-10,45; -1,75</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 10,23</t>
+          <t>-3,49; 10,58</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,3; -1,83</t>
+          <t>-10,57; -1,72</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-77,24; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 500,41</t>
+          <t>-58,98; 505,2</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,27</t>
+          <t>-5,67; 3,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -0,52</t>
+          <t>-8,09; -0,59</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -0,79</t>
+          <t>-8,55; -1,1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 1,14</t>
+          <t>-7,75; 1,0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 3,05</t>
+          <t>-6,85; 2,38</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 0,14</t>
+          <t>-8,58; 0,01</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,45</t>
+          <t>-5,7; 0,55</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -0,31</t>
+          <t>-5,98; -0,26</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,11; -1,59</t>
+          <t>-7,14; -1,6</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 107,12</t>
+          <t>-68,07; 96,96</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-92,15; 0,77</t>
+          <t>-94,06; -2,0</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-93,67; -9,51</t>
+          <t>-93,9; -11,83</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-80,01; 44,86</t>
+          <t>-77,78; 29,58</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-70,34; 75,1</t>
+          <t>-70,59; 56,79</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-83,04; 7,25</t>
+          <t>-80,65; 9,86</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 11,72</t>
+          <t>-67,46; 13,87</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-75,59; 2,93</t>
+          <t>-74,03; -0,06</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-82,41; -29,84</t>
+          <t>-82,06; -26,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,75</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-11,31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-9,75</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-14,51</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-5,38</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,47</t>
+          <t>-8,14</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 0,06</t>
+          <t>-13,38; 19,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,32; 4,93</t>
+          <t>-14,54; 23,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,72; -4,62</t>
+          <t>-28,22; 7,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 19,81</t>
+          <t>-34,17; 1,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 22,71</t>
+          <t>-28,2; 5,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 7,32</t>
+          <t>-35,02; -4,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 5,59</t>
+          <t>-18,58; 5,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 9,99</t>
+          <t>-15,35; 8,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,75; -0,52</t>
+          <t>-21,63; -0,03</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-26,21%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-77,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-67,23%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>80,16%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-27,89%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-80,64%</t>
+          <t>-77,51%</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-91,69; 292,88</t>
+          <t>-87,89; 273,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-7,59</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-7,59</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-3,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,95</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-3,95</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-7,59</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-7,59</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 0,0</t>
+          <t>-15,8; 9,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 0,0</t>
+          <t>-24,58; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 0,0</t>
+          <t>-23,57; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 9,79</t>
+          <t>-19,72; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 0,0</t>
+          <t>-20,37; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 0,0</t>
+          <t>-20,65; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 4,82</t>
+          <t>-12,25; 4,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,65; -1,76</t>
+          <t>-17,19; 0,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,7; -1,76</t>
+          <t>-15,44; 0,0</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-21,26%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-21,26%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-5,97</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-5,97</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-5,97</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-7,35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-12,05</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,81</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,97</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-5,97</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,97</t>
+          <t>-8,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,7</t>
+          <t>-7,31</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 7,52</t>
+          <t>-29,6; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 0,0</t>
+          <t>-29,64; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 9,55</t>
+          <t>-30,62; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 0,0</t>
+          <t>-30,52; 7,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 0,0</t>
+          <t>-36,13; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 0,0</t>
+          <t>-31,23; 4,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 0,79</t>
+          <t>-21,14; 0,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 0,0</t>
+          <t>-24,51; -2,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 2,25</t>
+          <t>-20,2; 0,68</t>
         </is>
       </c>
     </row>
@@ -1162,24 +1162,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-60,96%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-56,49%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-68,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-73,13%</t>
+          <t>-79,79%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-5,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,18</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-3,18</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-5,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 4,73</t>
+          <t>-24,64; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 0,0</t>
+          <t>-27,11; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 0,0</t>
+          <t>-25,11; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 0,0</t>
+          <t>-10,69; 4,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 0,0</t>
+          <t>-15,16; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 0,0</t>
+          <t>-16,39; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 2,34</t>
+          <t>-12,4; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 0,0</t>
+          <t>-13,26; 0,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 0,0</t>
+          <t>-13,78; 0,0</t>
         </is>
       </c>
     </row>
@@ -1378,22 +1378,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-27,93%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1488,34 +1488,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8,64</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,5</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,0</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2,52</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>4,63</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,34</t>
+          <t>0,0; 12,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,72</t>
+          <t>0,0; 17,09</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-7,23</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-11,16</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-11,16</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-8,84</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-15,64</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-15,64</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-7,23</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-11,16</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-11,16</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 10,78</t>
+          <t>-28,49; 5,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-38,32; -4,93</t>
+          <t>-37,02; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-38,32; -4,93</t>
+          <t>-33,83; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 6,03</t>
+          <t>-31,5; 12,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 0,0</t>
+          <t>-38,11; -4,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 0,0</t>
+          <t>-38,11; -4,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 4,23</t>
+          <t>-22,71; 2,33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-27,68; -5,36</t>
+          <t>-29,8; -5,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-27,34; -5,23</t>
+          <t>-27,92; -5,33</t>
         </is>
       </c>
     </row>
@@ -1810,22 +1810,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-64,77%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-56,53%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-64,77%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 95,6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-5,45</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,54</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-5,16</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>15,61</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>4,95</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>6,57</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-5,45</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,08</t>
+          <t>6,43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,41; 28,76</t>
+          <t>-18,84; 7,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,22</t>
+          <t>-16,03; 21,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,38; 16,92</t>
+          <t>-19,48; 7,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 5,66</t>
+          <t>5,35; 29,62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 21,04</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 8,88</t>
+          <t>1,3; 19,42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 14,49</t>
+          <t>-5,16; 14,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 12,83</t>
+          <t>-7,97; 14,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 9,03</t>
+          <t>-8,03; 8,61</t>
         </is>
       </c>
     </row>
@@ -2026,34 +2026,34 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-41,32%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-11,69%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-39,07%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-41,32%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-11,69%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-30,88%</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>61,44%</t>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 191,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,43; 217,65</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2099,27 +2099,27 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 442,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-85,59; 185,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 562,04</t>
+          <t>-46,22; 587,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 433,19</t>
+          <t>-100,0; 500,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-68,38; 292,05</t>
+          <t>-71,38; 378,94</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-5,01</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>5,66</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-5,01</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-4,11</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-4,11</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>5,66</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 0,0</t>
+          <t>-13,44; -1,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 9,47</t>
+          <t>-4,37; 18,79</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 0,0</t>
+          <t>-12,89; -1,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -1,51</t>
+          <t>-13,16; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 18,87</t>
+          <t>-6,81; 9,06</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -1,52</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -1,75</t>
+          <t>-9,91; -1,63</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 10,58</t>
+          <t>-2,97; 11,85</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,57; -1,72</t>
+          <t>-9,72; -1,63</t>
         </is>
       </c>
     </row>
@@ -2247,22 +2247,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>112,92%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
           <t>5,91%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>112,92%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-58,98; 505,2</t>
+          <t>-58,95; 519,71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-3,43</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-4,14</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-3,94</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-3,43</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-4,07</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,06</t>
+          <t>-7,95; 0,97</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -0,59</t>
+          <t>-7,62; 1,96</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -1,1</t>
+          <t>-8,83; -0,21</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,0</t>
+          <t>-5,81; 2,86</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 2,38</t>
+          <t>-8,3; -0,57</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,01</t>
+          <t>-7,88; -0,72</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,55</t>
+          <t>-5,39; 0,59</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -0,26</t>
+          <t>-6,15; -0,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -1,6</t>
+          <t>-7,02; -1,43</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-47,16%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-30,72%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-56,91%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-23,2%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-67,84%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-71,93%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-47,16%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-30,72%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-54,1%</t>
+          <t>-68,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-62,15%</t>
+          <t>-61,75%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 96,96</t>
+          <t>-81,08; 34,68</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-94,06; -2,0</t>
+          <t>-75,28; 48,75</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-93,9; -11,83</t>
+          <t>-84,66; 3,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-77,78; 29,58</t>
+          <t>-69,25; 90,41</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-70,59; 56,79</t>
+          <t>-93,58; -1,78</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-80,65; 9,86</t>
+          <t>-93,91; 7,05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-67,46; 13,87</t>
+          <t>-64,06; 15,17</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-74,03; -0,06</t>
+          <t>-74,82; -2,17</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-82,06; -26,89</t>
+          <t>-82,02; -21,23</t>
         </is>
       </c>
     </row>
